--- a/OutPut/descomposicion_resultados.xlsx
+++ b/OutPut/descomposicion_resultados.xlsx
@@ -13,30 +13,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t xml:space="preserve">periodo</t>
+    <t xml:space="preserve">contribucion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contribucion_porcentual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">edad</t>
   </si>
   <si>
     <t xml:space="preserve">sexo</t>
   </si>
   <si>
-    <t xml:space="preserve">dif_e0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2010-2019</t>
+    <t xml:space="preserve">periodo</t>
   </si>
   <si>
     <t xml:space="preserve">m</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">2010-2019</t>
   </si>
   <si>
     <t xml:space="preserve">f</t>
   </si>
   <si>
     <t xml:space="preserve">2019-2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dif_e0</t>
   </si>
 </sst>
 </file>
@@ -364,7 +370,1181 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.0208997987436603</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1.51823912693795</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.022000442115781</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1.51823912693795</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.101392098946954</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1.51823912693795</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.124758107669583</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1.51823912693795</v>
+      </c>
+      <c r="C5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.135033466653343</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.51823912693795</v>
+      </c>
+      <c r="C6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.135944910695604</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1.51823912693795</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.0629107746811631</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1.51823912693795</v>
+      </c>
+      <c r="C8" t="n">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>-0.0216923905255272</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1.51823912693795</v>
+      </c>
+      <c r="C9" t="n">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0.0158766052022536</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1.51823912693795</v>
+      </c>
+      <c r="C10" t="n">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.144207768084257</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1.51823912693795</v>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0.113347420957084</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1.51823912693795</v>
+      </c>
+      <c r="C12" t="n">
+        <v>55</v>
+      </c>
+      <c r="D12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.178814875196636</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1.51823912693795</v>
+      </c>
+      <c r="C13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D13" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.142559004244823</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1.51823912693795</v>
+      </c>
+      <c r="C14" t="n">
+        <v>65</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0.143079854304428</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1.51823912693795</v>
+      </c>
+      <c r="C15" t="n">
+        <v>70</v>
+      </c>
+      <c r="D15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0.0416369983220327</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1.51823912693795</v>
+      </c>
+      <c r="C16" t="n">
+        <v>75</v>
+      </c>
+      <c r="D16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0.0141552944539315</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1.51823912693795</v>
+      </c>
+      <c r="C17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0.001656456848303</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1.51823912693795</v>
+      </c>
+      <c r="C18" t="n">
+        <v>85</v>
+      </c>
+      <c r="D18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0.0255608899099918</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1.55051545570052</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>0.0285771806766624</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1.55051545570052</v>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>0.119056288173094</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1.55051545570052</v>
+      </c>
+      <c r="C21" t="n">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>0.133879647750942</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1.55051545570052</v>
+      </c>
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>0.140210728143958</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1.55051545570052</v>
+      </c>
+      <c r="C23" t="n">
+        <v>25</v>
+      </c>
+      <c r="D23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>0.130727105509255</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1.55051545570052</v>
+      </c>
+      <c r="C24" t="n">
+        <v>30</v>
+      </c>
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>0.0669211774969602</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1.55051545570052</v>
+      </c>
+      <c r="C25" t="n">
+        <v>35</v>
+      </c>
+      <c r="D25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>0.00556215627140205</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1.55051545570052</v>
+      </c>
+      <c r="C26" t="n">
+        <v>40</v>
+      </c>
+      <c r="D26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>0.0124264100138935</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1.55051545570052</v>
+      </c>
+      <c r="C27" t="n">
+        <v>45</v>
+      </c>
+      <c r="D27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>0.108916609012266</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1.55051545570052</v>
+      </c>
+      <c r="C28" t="n">
+        <v>50</v>
+      </c>
+      <c r="D28" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>0.0974639846356462</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1.55051545570052</v>
+      </c>
+      <c r="C29" t="n">
+        <v>55</v>
+      </c>
+      <c r="D29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>0.122779427835622</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1.55051545570052</v>
+      </c>
+      <c r="C30" t="n">
+        <v>60</v>
+      </c>
+      <c r="D30" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>0.170697937423043</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1.55051545570052</v>
+      </c>
+      <c r="C31" t="n">
+        <v>65</v>
+      </c>
+      <c r="D31" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>0.180201621230368</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1.55051545570052</v>
+      </c>
+      <c r="C32" t="n">
+        <v>70</v>
+      </c>
+      <c r="D32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>0.171285695683279</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1.55051545570052</v>
+      </c>
+      <c r="C33" t="n">
+        <v>75</v>
+      </c>
+      <c r="D33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>0.0338497373683829</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1.55051545570052</v>
+      </c>
+      <c r="C34" t="n">
+        <v>80</v>
+      </c>
+      <c r="D34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0.100424848615905</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1.55051545570052</v>
+      </c>
+      <c r="C35" t="n">
+        <v>85</v>
+      </c>
+      <c r="D35" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>-0.0112441400492619</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0.330400727026353</v>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0.0213844429278947</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0.330400727026353</v>
+      </c>
+      <c r="C37" t="n">
+        <v>10</v>
+      </c>
+      <c r="D37" t="s">
+        <v>5</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0.0335801058123834</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0.330400727026353</v>
+      </c>
+      <c r="C38" t="n">
+        <v>15</v>
+      </c>
+      <c r="D38" t="s">
+        <v>5</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>-0.0733523070505417</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0.330400727026353</v>
+      </c>
+      <c r="C39" t="n">
+        <v>20</v>
+      </c>
+      <c r="D39" t="s">
+        <v>5</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>-0.0933768278221562</v>
+      </c>
+      <c r="B40" t="n">
+        <v>0.330400727026353</v>
+      </c>
+      <c r="C40" t="n">
+        <v>25</v>
+      </c>
+      <c r="D40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>-0.152681878444342</v>
+      </c>
+      <c r="B41" t="n">
+        <v>0.330400727026353</v>
+      </c>
+      <c r="C41" t="n">
+        <v>30</v>
+      </c>
+      <c r="D41" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>-0.235280607707091</v>
+      </c>
+      <c r="B42" t="n">
+        <v>0.330400727026353</v>
+      </c>
+      <c r="C42" t="n">
+        <v>35</v>
+      </c>
+      <c r="D42" t="s">
+        <v>5</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>-0.279111237941546</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0.330400727026353</v>
+      </c>
+      <c r="C43" t="n">
+        <v>40</v>
+      </c>
+      <c r="D43" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>-0.327284381208167</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0.330400727026353</v>
+      </c>
+      <c r="C44" t="n">
+        <v>45</v>
+      </c>
+      <c r="D44" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>-0.3809291894346</v>
+      </c>
+      <c r="B45" t="n">
+        <v>0.330400727026353</v>
+      </c>
+      <c r="C45" t="n">
+        <v>50</v>
+      </c>
+      <c r="D45" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>-0.454442547846434</v>
+      </c>
+      <c r="B46" t="n">
+        <v>0.330400727026353</v>
+      </c>
+      <c r="C46" t="n">
+        <v>55</v>
+      </c>
+      <c r="D46" t="s">
+        <v>5</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>-0.534350842490973</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0.330400727026353</v>
+      </c>
+      <c r="C47" t="n">
+        <v>60</v>
+      </c>
+      <c r="D47" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>-0.388343512497634</v>
+      </c>
+      <c r="B48" t="n">
+        <v>0.330400727026353</v>
+      </c>
+      <c r="C48" t="n">
+        <v>65</v>
+      </c>
+      <c r="D48" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>-0.326600717371723</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0.330400727026353</v>
+      </c>
+      <c r="C49" t="n">
+        <v>70</v>
+      </c>
+      <c r="D49" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>-0.156355661024183</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0.330400727026353</v>
+      </c>
+      <c r="C50" t="n">
+        <v>75</v>
+      </c>
+      <c r="D50" t="s">
+        <v>5</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>-0.0380668000590887</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0.330400727026353</v>
+      </c>
+      <c r="C51" t="n">
+        <v>80</v>
+      </c>
+      <c r="D51" t="s">
+        <v>5</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>-0.00672649683224637</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0.330400727026353</v>
+      </c>
+      <c r="C52" t="n">
+        <v>85</v>
+      </c>
+      <c r="D52" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>-0.0147925147147557</v>
+      </c>
+      <c r="B53" t="n">
+        <v>0.385657753434351</v>
+      </c>
+      <c r="C53" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>0.00449194329211549</v>
+      </c>
+      <c r="B54" t="n">
+        <v>0.385657753434351</v>
+      </c>
+      <c r="C54" t="n">
+        <v>10</v>
+      </c>
+      <c r="D54" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>0.037434070389945</v>
+      </c>
+      <c r="B55" t="n">
+        <v>0.385657753434351</v>
+      </c>
+      <c r="C55" t="n">
+        <v>15</v>
+      </c>
+      <c r="D55" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>-0.0116563919937614</v>
+      </c>
+      <c r="B56" t="n">
+        <v>0.385657753434351</v>
+      </c>
+      <c r="C56" t="n">
+        <v>20</v>
+      </c>
+      <c r="D56" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>-0.0840321621920109</v>
+      </c>
+      <c r="B57" t="n">
+        <v>0.385657753434351</v>
+      </c>
+      <c r="C57" t="n">
+        <v>25</v>
+      </c>
+      <c r="D57" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>-0.108143723573769</v>
+      </c>
+      <c r="B58" t="n">
+        <v>0.385657753434351</v>
+      </c>
+      <c r="C58" t="n">
+        <v>30</v>
+      </c>
+      <c r="D58" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>-0.211178230788253</v>
+      </c>
+      <c r="B59" t="n">
+        <v>0.385657753434351</v>
+      </c>
+      <c r="C59" t="n">
+        <v>35</v>
+      </c>
+      <c r="D59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>-0.208635362383985</v>
+      </c>
+      <c r="B60" t="n">
+        <v>0.385657753434351</v>
+      </c>
+      <c r="C60" t="n">
+        <v>40</v>
+      </c>
+      <c r="D60" t="s">
+        <v>7</v>
+      </c>
+      <c r="E60" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>-0.273772382520779</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0.385657753434351</v>
+      </c>
+      <c r="C61" t="n">
+        <v>45</v>
+      </c>
+      <c r="D61" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>-0.282189544672574</v>
+      </c>
+      <c r="B62" t="n">
+        <v>0.385657753434351</v>
+      </c>
+      <c r="C62" t="n">
+        <v>50</v>
+      </c>
+      <c r="D62" t="s">
+        <v>7</v>
+      </c>
+      <c r="E62" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>-0.408765193980371</v>
+      </c>
+      <c r="B63" t="n">
+        <v>0.385657753434351</v>
+      </c>
+      <c r="C63" t="n">
+        <v>55</v>
+      </c>
+      <c r="D63" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>-0.513934733430225</v>
+      </c>
+      <c r="B64" t="n">
+        <v>0.385657753434351</v>
+      </c>
+      <c r="C64" t="n">
+        <v>60</v>
+      </c>
+      <c r="D64" t="s">
+        <v>7</v>
+      </c>
+      <c r="E64" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>-0.502075512467335</v>
+      </c>
+      <c r="B65" t="n">
+        <v>0.385657753434351</v>
+      </c>
+      <c r="C65" t="n">
+        <v>65</v>
+      </c>
+      <c r="D65" t="s">
+        <v>7</v>
+      </c>
+      <c r="E65" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>-0.476869740812781</v>
+      </c>
+      <c r="B66" t="n">
+        <v>0.385657753434351</v>
+      </c>
+      <c r="C66" t="n">
+        <v>70</v>
+      </c>
+      <c r="D66" t="s">
+        <v>7</v>
+      </c>
+      <c r="E66" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>-0.351659615326123</v>
+      </c>
+      <c r="B67" t="n">
+        <v>0.385657753434351</v>
+      </c>
+      <c r="C67" t="n">
+        <v>75</v>
+      </c>
+      <c r="D67" t="s">
+        <v>7</v>
+      </c>
+      <c r="E67" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>-0.143763471421035</v>
+      </c>
+      <c r="B68" t="n">
+        <v>0.385657753434351</v>
+      </c>
+      <c r="C68" t="n">
+        <v>80</v>
+      </c>
+      <c r="D68" t="s">
+        <v>7</v>
+      </c>
+      <c r="E68" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>-0.286116014886389</v>
+      </c>
+      <c r="B69" t="n">
+        <v>0.385657753434351</v>
+      </c>
+      <c r="C69" t="n">
+        <v>85</v>
+      </c>
+      <c r="D69" t="s">
+        <v>7</v>
+      </c>
+      <c r="E69" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -377,57 +1557,57 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.3765814865944</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.6485414457506</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-3.4031825990398</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-3.83565858148209</v>
       </c>
     </row>
   </sheetData>
